--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-effet-indesirable.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-effet-indesirable.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AdverseEvent - Effet indésirable</t>
+    <t>AdverseEvent - Fr Effet indésirable</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -684,7 +684,7 @@
     <t>Describes the type of outcome from the adverse event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/adverse-event-outcome</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-evolution-cisis</t>
   </si>
   <si>
     <t>AdverseEvent.recorder</t>
@@ -723,7 +723,7 @@
 </t>
   </si>
   <si>
-    <t>The suspected agent causing the adverse event</t>
+    <t>Agent soupçonné d’être à l’origine de l’événement indésirable</t>
   </si>
   <si>
     <t>Describes the entity that is suspected to have caused the adverse event.</t>
@@ -781,7 +781,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document)
 </t>
   </si>
   <si>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-effet-indesirable.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-effet-indesirable.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
